--- a/data/b2_indio/B2 Índio 07-2026.xlsx
+++ b/data/b2_indio/B2 Índio 07-2026.xlsx
@@ -4851,20 +4851,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>3658.95</v>
+        <v>52088.57</v>
       </c>
     </row>
     <row r="3">
@@ -4873,16 +4873,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>52443.92</v>
+        <v>1690.68</v>
       </c>
     </row>
     <row r="4">
@@ -4891,34 +4891,34 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>918.38</v>
+        <v>2191.94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46208</v>
+        <v>46210</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>2378.96</v>
+        <v>899.24</v>
       </c>
     </row>
     <row r="6">
@@ -4950,11 +4950,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2588.81</v>
+        <v>1991.9</v>
       </c>
     </row>
     <row r="8">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3204.58</v>
+        <v>2995.79</v>
       </c>
     </row>
     <row r="9">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1944.22</v>
+        <v>1898.4</v>
       </c>
     </row>
     <row r="10">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9547.15</v>
+        <v>8640.809999999999</v>
       </c>
     </row>
     <row r="11">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1489.93</v>
+        <v>1535.32</v>
       </c>
     </row>
     <row r="12">
@@ -5053,57 +5053,57 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1898.96</v>
+        <v>3121.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3257.6</v>
+        <v>18133.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>18082.41</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46229</v>
+        <v>46227</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -5112,11 +5112,11 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1229.76</v>
+        <v>1136.95</v>
       </c>
     </row>
     <row r="17">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3127.85</v>
+        <v>3325.27</v>
       </c>
     </row>
     <row r="18">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2406.39</v>
+        <v>2415.76</v>
       </c>
     </row>
   </sheetData>
